--- a/Analysis_Output/WCAG22_AA_Final_Report_Analysis.xlsx
+++ b/Analysis_Output/WCAG22_AA_Final_Report_Analysis.xlsx
@@ -155,8 +155,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DocumentAnalysisTable" displayName="DocumentAnalysisTable" ref="A1:N6" headerRowCount="1">
-  <autoFilter ref="A1:N6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DocumentAnalysisTable" displayName="DocumentAnalysisTable" ref="A1:N17" headerRowCount="1">
+  <autoFilter ref="A1:N17"/>
   <tableColumns count="14">
     <tableColumn id="1" name="PDF Name"/>
     <tableColumn id="2" name="Overall Status"/>
@@ -178,8 +178,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="IssueBreakdownTable" displayName="IssueBreakdownTable" ref="A1:C21" headerRowCount="1">
-  <autoFilter ref="A1:C21"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="IssueBreakdownTable" displayName="IssueBreakdownTable" ref="A1:C22" headerRowCount="1">
+  <autoFilter ref="A1:C22"/>
   <tableColumns count="3">
     <tableColumn id="1" name="Rule"/>
     <tableColumn id="2" name="Category"/>
@@ -190,8 +190,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="WCAGBreakdownTable" displayName="WCAGBreakdownTable" ref="A1:B7" headerRowCount="1">
-  <autoFilter ref="A1:B7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="WCAGBreakdownTable" displayName="WCAGBreakdownTable" ref="A1:B8" headerRowCount="1">
+  <autoFilter ref="A1:B8"/>
   <tableColumns count="2">
     <tableColumn id="1" name="WCAG Criterion"/>
     <tableColumn id="2" name="Failed Issue Count (Unique)"/>
@@ -223,8 +223,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="ManualReviewTable" displayName="ManualReviewTable" ref="A1:B5" headerRowCount="1">
-  <autoFilter ref="A1:B5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="ManualReviewTable" displayName="ManualReviewTable" ref="A1:B11" headerRowCount="1">
+  <autoFilter ref="A1:B11"/>
   <tableColumns count="2">
     <tableColumn id="1" name="Manual Review Item"/>
     <tableColumn id="2" name="Count Across PDFs"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-25T12:06:30</t>
+          <t>2026-03-25T16:20:49</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>33.75</v>
+        <v>75.98</v>
       </c>
     </row>
     <row r="5">
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.2</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="6">
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -631,7 +631,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>CCG0125.json, CCJ0031.json, CCG0613.json, CCG0646.json, CCG0815.json, GCR2403.json, IRP1101.json, MNO705.json, MSA902.json</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -653,7 +653,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>CCG0813.json, CCG0650.json</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CCP1000.json, CCP1003.json, CCP1004.json, CCP1005.json, CCP1007.json</t>
+          <t>CCJ0700.json, CCG0134.json, CCG0135.json, CCG0136.json, CCG0137.json</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -787,7 +787,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CCP1000.json</t>
+          <t>CCJ0700.json</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -811,10 +811,10 @@
         <v>21</v>
       </c>
       <c r="H2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -823,7 +823,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -832,14 +832,14 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Tagged form fields (2), Tagged PDF (1), Title (1), Tagged content (1), Tagged annotations (1)</t>
+          <t>Tagged form fields (2), Tagged PDF (1), Primary language (1), Title (1), Tagged content (1)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CCP1003.json</t>
+          <t>CCG0134.json</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -848,25 +848,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>34.38</v>
+        <v>71.88</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H3" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -875,7 +875,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -884,14 +884,14 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Tagged form fields (2), Tagged PDF (1), Title (1), Tagged content (1), Tab order (1)</t>
+          <t>Tagged form fields (2), Tagged PDF (1), Title (1), Tagged content (1), Tagged annotations (1)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CCP1004.json</t>
+          <t>CCG0135.json</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -900,25 +900,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>34.38</v>
+        <v>71.88</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E4" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H4" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -927,7 +927,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -936,14 +936,14 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Tagged form fields (2), Tagged PDF (1), Title (1), Tagged content (1), Tab order (1)</t>
+          <t>Tagged form fields (2), Tagged PDF (1), Title (1), Tagged content (1), Tagged annotations (1)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CCP1005.json</t>
+          <t>CCG0136.json</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -952,25 +952,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>34.38</v>
+        <v>71.88</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E5" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H5" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -979,7 +979,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -988,14 +988,14 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Tagged form fields (2), Tagged PDF (1), Title (1), Tagged content (1), Tab order (1)</t>
+          <t>Tagged form fields (2), Tagged PDF (1), Title (1), Tagged content (1), Tagged annotations (1)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CCP1007.json</t>
+          <t>CCG0137.json</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1004,48 +1004,620 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>34.38</v>
+        <v>71.88</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E6" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H6" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>25</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Tagged form fields (2), Tagged PDF (1), Title (1), Tagged content (1), Tagged annotations (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CCG0813.json</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>65.62</v>
+      </c>
+      <c r="D7" t="n">
+        <v>21</v>
+      </c>
+      <c r="E7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>7</v>
+      </c>
+      <c r="H7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>24</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Tagged form fields (2), Title (1), Tab order (1), Field descriptions (1), Headers (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CCG0650.json</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="D8" t="n">
+        <v>22</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>22</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Tagged form fields (2), Title (1), Tagged annotations (1), Tab order (1), Field descriptions (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CCG0125.json</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>78.12</v>
+      </c>
+      <c r="D9" t="n">
+        <v>25</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>10</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Title (1), Field descriptions (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CCJ0031.json</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>78.12</v>
+      </c>
+      <c r="D10" t="n">
+        <v>25</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>10</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Title (1), Tab order (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CCG0613.json</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="D11" t="n">
+        <v>26</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>7</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Title (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CCG0646.json</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="D12" t="n">
+        <v>26</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>7</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Title (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CCG0815.json</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="D13" t="n">
+        <v>26</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>7</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Title (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>GCR2403.json</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>90.62</v>
+      </c>
+      <c r="D14" t="n">
+        <v>29</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>4</v>
       </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>58</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Large</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Tagged form fields (2), Tagged PDF (1), Title (1), Tagged content (1), Tab order (1)</t>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Title (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>IRP1101.json</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>90.62</v>
+      </c>
+      <c r="D15" t="n">
+        <v>29</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>4</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Title (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MNO705.json</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>90.62</v>
+      </c>
+      <c r="D16" t="n">
+        <v>29</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>4</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Title (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MSA902.json</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>90.62</v>
+      </c>
+      <c r="D17" t="n">
+        <v>29</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>4</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Title (1)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C6">
+  <conditionalFormatting sqref="C2:C17">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -1070,7 +1642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1098,52 +1670,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Tagged form fields</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Forms</t>
+          <t>Document</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Tagged PDF</t>
+          <t>Tagged form fields</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Forms</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Field descriptions</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Forms</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tagged content</t>
+          <t>Tab order</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1152,18 +1724,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tab order</t>
+          <t>Tagged PDF</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Page Content</t>
+          <t>Document</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1173,12 +1745,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Field descriptions</t>
+          <t>Tagged content</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Forms</t>
+          <t>Page Content</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1188,12 +1760,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Figures alternate text</t>
+          <t>Tagged annotations</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Alternate Text</t>
+          <t>Page Content</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1203,52 +1775,52 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nested alternate text</t>
+          <t>Headers</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Alternate Text</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Associated with content</t>
+          <t>Summary</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alternate Text</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Hides annotation</t>
+          <t>Primary language</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Alternate Text</t>
+          <t>Document</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Other elements alternate text</t>
+          <t>Figures alternate text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1257,73 +1829,73 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Rows</t>
+          <t>Nested alternate text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Alternate Text</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TH and TD</t>
+          <t>Associated with content</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Alternate Text</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Headers</t>
+          <t>Hides annotation</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Alternate Text</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Regularity</t>
+          <t>Other elements alternate text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Alternate Text</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Summary</t>
+          <t>Rows</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1332,66 +1904,81 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>List items</t>
+          <t>TH and TD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lists</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Lbl and LBody</t>
+          <t>Regularity</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lists</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Appropriate nesting</t>
+          <t>List items</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Headings</t>
+          <t>Lists</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tagged annotations</t>
+          <t>Lbl and LBody</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Page Content</t>
+          <t>Lists</t>
         </is>
       </c>
       <c r="C21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Appropriate nesting</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Headings</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1409,7 +1996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1435,27 +2022,27 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1.1.1</t>
+          <t>2.4.2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2.4.2</t>
+          <t>3.3.2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -1465,7 +2052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -1475,17 +2062,27 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3.3.2</t>
+          <t>1.1.1</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>3.1.1</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1524,51 +2121,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alternate Text</t>
+          <t>Document</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Forms</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Forms</t>
+          <t>Page Content</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Page Content</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Alternate Text</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -1578,7 +2175,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -1588,7 +2185,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1631,7 +2228,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3">
@@ -1641,7 +2238,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1658,7 +2255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -1684,7 +2281,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -1694,7 +2291,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -1704,7 +2301,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -1714,7 +2311,67 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>{'rule': 'Screen flicker', 'category': 'Page Content', 'status': 'Needs manual check', 'wcag': 'Unknown', 'wcag_name': 'Unknown', 'wcag_level': 'Unknown', 'impact': 'Medium', 'recommendation': {'issue': 'Unknown accessibility issue', 'fix': ['Review manually as per WCAG guidelines'], 'priority': 'Medium', 'automation_possible': False}}</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Screen flicker</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>{'rule': 'Scripts', 'category': 'Page Content', 'status': 'Needs manual check', 'wcag': 'Unknown', 'wcag_name': 'Unknown', 'wcag_level': 'Unknown', 'impact': 'Medium', 'recommendation': {'issue': 'Unknown accessibility issue', 'fix': ['Review manually as per WCAG guidelines'], 'priority': 'Medium', 'automation_possible': False}}</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Scripts</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>{'rule': 'Timed responses', 'category': 'Page Content', 'status': 'Needs manual check', 'wcag': 'Unknown', 'wcag_name': 'Unknown', 'wcag_level': 'Unknown', 'impact': 'Medium', 'recommendation': {'issue': 'Unknown accessibility issue', 'fix': ['Review manually as per WCAG guidelines'], 'priority': 'Medium', 'automation_possible': False}}</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Timed responses</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
